--- a/downloads/free-resources/ahqs-risk-register-template.xlsx
+++ b/downloads/free-resources/ahqs-risk-register-template.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
+  <workbookProtection workbookPassword="AF18" lockStructure="1" lockWindows="0"/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
@@ -744,7 +744,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -863,7 +863,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -982,7 +982,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -1104,7 +1104,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1194,7 +1194,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1227,7 +1227,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -1328,7 +1328,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -1417,7 +1417,7 @@
                   </a:defRPr>
                 </a:pPr>
                 <a:r>
-                  <a:t/>
+                  <a:t>None</a:t>
                 </a:r>
               </a:p>
             </txPr>
@@ -1509,7 +1509,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1599,7 +1599,7 @@
               </a:defRPr>
             </a:pPr>
             <a:r>
-              <a:t/>
+              <a:t>None</a:t>
             </a:r>
           </a:p>
         </txPr>
@@ -1632,7 +1632,7 @@
             </a:defRPr>
           </a:pPr>
           <a:r>
-            <a:t/>
+            <a:t>None</a:t>
           </a:r>
         </a:p>
       </txPr>
@@ -1941,7 +1941,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B9:C34"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="31" min="1" max="1"/>
@@ -1949,6 +1949,14 @@
     <col width="3" customWidth="1" style="31" min="3" max="3"/>
   </cols>
   <sheetData>
+    <row r="1"/>
+    <row r="2"/>
+    <row r="3"/>
+    <row r="4"/>
+    <row r="5"/>
+    <row r="6"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9" ht="26.8" customHeight="1" s="32">
       <c r="B9" s="33" t="inlineStr">
         <is>
@@ -1963,6 +1971,7 @@
         </is>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="32">
       <c r="B12" s="35" t="n"/>
       <c r="C12" s="35" t="n"/>
@@ -1974,6 +1983,7 @@
         </is>
       </c>
     </row>
+    <row r="14"/>
     <row r="15" ht="16.15" customHeight="1" s="32">
       <c r="B15" s="37" t="inlineStr">
         <is>
@@ -2023,6 +2033,7 @@
         </is>
       </c>
     </row>
+    <row r="22"/>
     <row r="23" ht="16.15" customHeight="1" s="32">
       <c r="B23" s="37" t="inlineStr">
         <is>
@@ -2072,6 +2083,7 @@
         </is>
       </c>
     </row>
+    <row r="30"/>
     <row r="31" ht="16.15" customHeight="1" s="32">
       <c r="B31" s="37" t="inlineStr">
         <is>
@@ -2086,6 +2098,7 @@
         </is>
       </c>
     </row>
+    <row r="33"/>
     <row r="34" ht="15" customHeight="1" s="32">
       <c r="B34" s="40" t="inlineStr">
         <is>
@@ -2094,6 +2107,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="AF18"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -2274,6 +2288,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="AF18"/>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="0" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -3644,6 +3659,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="AF18"/>
   <autoFilter ref="A1:R41"/>
   <conditionalFormatting sqref="H2:H41">
     <cfRule type="cellIs" rank="0" priority="2" equalAverage="0" operator="greaterThanOrEqual" aboveAverage="0" dxfId="9" text="" percent="0" bottom="0">
@@ -3703,7 +3719,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:G12"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="31" min="1" max="1"/>
@@ -3711,6 +3727,7 @@
     <col width="16" customWidth="1" style="31" min="3" max="7"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="27.75" customHeight="1" s="32">
       <c r="B2" s="48" t="inlineStr">
         <is>
@@ -3718,6 +3735,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1" s="32">
       <c r="B4" s="49" t="inlineStr">
         <is>
@@ -3862,6 +3880,7 @@
         <v>5</v>
       </c>
     </row>
+    <row r="11"/>
     <row r="12" ht="15" customHeight="1" s="32">
       <c r="B12" s="54" t="inlineStr">
         <is>
@@ -3890,6 +3909,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="AF18"/>
   <mergeCells count="2">
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B4:C4"/>
@@ -3906,13 +3926,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:L27"/>
+  <dimension ref="A1:L27"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="3" customWidth="1" style="31" min="1" max="1"/>
     <col width="14" customWidth="1" style="31" min="2" max="12"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2" ht="31.5" customHeight="1" s="32">
       <c r="B2" s="59" t="inlineStr">
         <is>
@@ -3920,6 +3941,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="21.75" customHeight="1" s="32">
       <c r="B4" s="60" t="inlineStr">
         <is>
@@ -3970,6 +3992,8 @@
       </c>
     </row>
     <row r="6" ht="19.5" customHeight="1" s="32"/>
+    <row r="7"/>
+    <row r="8"/>
     <row r="9" ht="24" customHeight="1" s="32">
       <c r="B9" s="62" t="inlineStr">
         <is>
@@ -4170,6 +4194,8 @@
         <v/>
       </c>
     </row>
+    <row r="20"/>
+    <row r="21"/>
     <row r="22" ht="24" customHeight="1" s="32">
       <c r="B22" s="62" t="inlineStr">
         <is>
@@ -4253,6 +4279,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="1" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="1" sort="1" password="AF18"/>
   <mergeCells count="13">
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="J4:K4"/>
